--- a/Shablon_upravlenia_IT_proektom_dlya_odnoy_komandy.xlsx
+++ b/Shablon_upravlenia_IT_proektom_dlya_odnoy_komandy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STUDENT\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STUDENT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68F18A1-C076-48F1-9790-648A71C38C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8F1F58-6C24-468E-AFCE-FD887C8481D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4095" yWindow="-180" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОБЗОР" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="162">
   <si>
     <t>PROJECT LAB  /  ПУЛЬТ КОМАНДЫ</t>
   </si>
@@ -516,6 +516,12 @@
   </si>
   <si>
     <t>Нехватка времени, отсутствие бюджета на разработку, ограниченные навыки и знания</t>
+  </si>
+  <si>
+    <t>Готово</t>
+  </si>
+  <si>
+    <t>Гибкий подход</t>
   </si>
 </sst>
 </file>
@@ -611,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -630,6 +636,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -897,38 +904,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
@@ -1024,7 +1031,7 @@
       </c>
       <c r="B22">
         <f>COUNTIF(ЭТАПЫ!D6:D23,"Готово")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1097,32 +1104,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -1238,13 +1245,13 @@
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1271,207 +1278,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="6" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
     </row>
     <row r="18" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="13" t="e">
+      <c r="B18" s="14" t="e">
         <f>-B12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1495,50 +1502,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
     </row>
     <row r="2" spans="1:12" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="29.1" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -3759,32 +3766,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="29.1" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -3817,9 +3824,11 @@
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>137</v>
+      </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6">
@@ -3833,10 +3842,14 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
@@ -4128,32 +4141,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="27" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="27" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="29.1" customHeight="1">
       <c r="A5" s="1" t="s">

--- a/Shablon_upravlenia_IT_proektom_dlya_odnoy_komandy.xlsx
+++ b/Shablon_upravlenia_IT_proektom_dlya_odnoy_komandy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STUDENT\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8F1F58-6C24-468E-AFCE-FD887C8481D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C95CE8-FEF5-48C4-B266-3ACF64AC889C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ОБЗОР" sheetId="1" r:id="rId1"/>
@@ -497,9 +497,6 @@
     <t>Быстрый поиск и бронирование свободного времени</t>
   </si>
   <si>
-    <t>Поставщик услуг может загрузить свои услуги. Клиент может забронировать дату и время</t>
-  </si>
-  <si>
     <t>Фильтры, поиск, категории</t>
   </si>
   <si>
@@ -522,6 +519,9 @@
   </si>
   <si>
     <t>Гибкий подход</t>
+  </si>
+  <si>
+    <t>Поставщик услуг может загрузить свои услуги, выставить свое расписание. Клиент может забронировать дату и время, и отменить</t>
   </si>
 </sst>
 </file>
@@ -617,7 +617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -645,6 +645,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1369,20 +1372,20 @@
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="B11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" spans="1:6" ht="33.950000000000003" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1394,7 +1397,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1406,7 +1409,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1418,7 +1421,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -1430,7 +1433,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -1442,7 +1445,7 @@
         <v>40</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -1464,21 +1467,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3824,7 +3827,7 @@
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>137</v>
@@ -3842,13 +3845,13 @@
         <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>137</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:6">
